--- a/output/roomself_excel/14334.xlsx
+++ b/output/roomself_excel/14334.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>937321</v>
+        <v>82272</v>
       </c>
       <c r="D2" t="n">
-        <v>20364</v>
+        <v>2452</v>
       </c>
       <c r="E2" t="n">
-        <v>1339</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>1140</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>8856</v>
+        <v>188992</v>
       </c>
       <c r="D3" t="n">
-        <v>760</v>
+        <v>3528</v>
       </c>
       <c r="E3" t="n">
-        <v>108</v>
+        <v>506</v>
       </c>
       <c r="F3" t="n">
-        <v>16</v>
+        <v>400</v>
       </c>
     </row>
     <row r="4">
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>12794</v>
+        <v>75211</v>
       </c>
       <c r="D4" t="n">
-        <v>924</v>
+        <v>2432</v>
       </c>
       <c r="E4" t="n">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -536,16 +536,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>15120</v>
+        <v>68121</v>
       </c>
       <c r="D5" t="n">
-        <v>992</v>
+        <v>2532</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>138</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>118</v>
       </c>
     </row>
     <row r="6">
@@ -554,20 +554,196 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>Bath</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>8856</v>
+      </c>
+      <c r="D6" t="n">
+        <v>760</v>
+      </c>
+      <c r="E6" t="n">
+        <v>108</v>
+      </c>
+      <c r="F6" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Bath</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>12794</v>
+      </c>
+      <c r="D7" t="n">
+        <v>924</v>
+      </c>
+      <c r="E7" t="n">
+        <v>101</v>
+      </c>
+      <c r="F7" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Bath</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>15120</v>
+      </c>
+      <c r="D8" t="n">
+        <v>992</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Hallway</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>222867</v>
+      </c>
+      <c r="D9" t="n">
+        <v>8488</v>
+      </c>
+      <c r="E9" t="n">
+        <v>622</v>
+      </c>
+      <c r="F9" t="n">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Hallway</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>5742</v>
+      </c>
+      <c r="D10" t="n">
+        <v>628</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="C11" t="n">
+        <v>110842</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2716</v>
+      </c>
+      <c r="E11" t="n">
+        <v>402</v>
+      </c>
+      <c r="F11" t="n">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>108945</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2996</v>
+      </c>
+      <c r="E12" t="n">
+        <v>387</v>
+      </c>
+      <c r="F12" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
         <v>48984</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D13" t="n">
         <v>1880</v>
       </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>74329</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2200</v>
+      </c>
+      <c r="E14" t="n">
+        <v>311</v>
+      </c>
+      <c r="F14" t="n">
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/14334.xlsx
+++ b/output/roomself_excel/14334.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:P14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,62 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_3</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_4</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_4</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_4</t>
         </is>
       </c>
     </row>
@@ -475,12 +525,26 @@
       <c r="D2" t="n">
         <v>2452</v>
       </c>
-      <c r="E2" t="n">
-        <v>0</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
-      </c>
+        <v>335</v>
+      </c>
+      <c r="G2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,12 +561,34 @@
       <c r="D3" t="n">
         <v>3528</v>
       </c>
-      <c r="E3" t="n">
-        <v>506</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>400</v>
-      </c>
+        <v>384</v>
+      </c>
+      <c r="G3" t="n">
+        <v>16</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>490</v>
+      </c>
+      <c r="J3" t="n">
+        <v>16</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,12 +605,18 @@
       <c r="D4" t="n">
         <v>2432</v>
       </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,12 +633,26 @@
       <c r="D5" t="n">
         <v>2532</v>
       </c>
-      <c r="E5" t="n">
-        <v>138</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F5" t="n">
-        <v>118</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="G5" t="n">
+        <v>16</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -563,12 +669,26 @@
       <c r="D6" t="n">
         <v>760</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
         <v>108</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>16</v>
       </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,12 +705,26 @@
       <c r="D7" t="n">
         <v>924</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
         <v>101</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>16</v>
       </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,12 +741,18 @@
       <c r="D8" t="n">
         <v>992</v>
       </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,11 +769,49 @@
       <c r="D9" t="n">
         <v>8488</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
         <v>622</v>
       </c>
-      <c r="F9" t="n">
-        <v>323</v>
+      <c r="G9" t="n">
+        <v>16</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>247</v>
+      </c>
+      <c r="J9" t="n">
+        <v>15</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>193</v>
+      </c>
+      <c r="M9" t="n">
+        <v>15</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
+        <v>45</v>
+      </c>
+      <c r="P9" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="10">
@@ -651,12 +829,18 @@
       <c r="D10" t="n">
         <v>628</v>
       </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,12 +857,34 @@
       <c r="D11" t="n">
         <v>2716</v>
       </c>
-      <c r="E11" t="n">
-        <v>402</v>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F11" t="n">
-        <v>301</v>
-      </c>
+        <v>285</v>
+      </c>
+      <c r="G11" t="n">
+        <v>16</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>386</v>
+      </c>
+      <c r="J11" t="n">
+        <v>16</v>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -695,12 +901,34 @@
       <c r="D12" t="n">
         <v>2996</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
         <v>387</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>16</v>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>279</v>
+      </c>
+      <c r="J12" t="n">
+        <v>15</v>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -717,12 +945,26 @@
       <c r="D13" t="n">
         <v>1880</v>
       </c>
-      <c r="E13" t="n">
-        <v>0</v>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="G13" t="n">
+        <v>15</v>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -739,12 +981,34 @@
       <c r="D14" t="n">
         <v>2200</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
         <v>311</v>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
         <v>16</v>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>239</v>
+      </c>
+      <c r="J14" t="n">
+        <v>15</v>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
